--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedOrganizationAbteilung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedOrganizationAbteilung.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="348">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedOrganizationAbteilung</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedOrganizationAbteilung</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -460,17 +460,14 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Organization.extension:kostenstelle</t>
-  </si>
-  <si>
-    <t>kostenstelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-kostenstelle}
+    <t>Organization.extension:Kostenstelle</t>
+  </si>
+  <si>
+    <t>Kostenstelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-Kostenstelle}
 </t>
-  </si>
-  <si>
-    <t>Kostenstelle</t>
   </si>
   <si>
     <t>MOPED Extension für akzeptierte Errors und Warnings</t>
@@ -2535,10 +2532,10 @@
         <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2621,14 +2618,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2650,16 +2647,16 @@
         <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2708,7 +2705,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2740,10 +2737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2766,17 +2763,17 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2813,7 +2810,7 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
@@ -2823,7 +2820,7 @@
         <v>140</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2832,36 +2829,36 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -2883,17 +2880,17 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2942,7 +2939,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2951,33 +2948,33 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3003,10 +3000,10 @@
         <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3057,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3066,19 +3063,19 @@
         <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -3089,14 +3086,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3118,13 +3115,13 @@
         <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="N15" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3165,7 +3162,7 @@
         <v>139</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>20</v>
@@ -3174,7 +3171,7 @@
         <v>140</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3195,7 +3192,7 @@
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3206,10 +3203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3235,16 +3232,16 @@
         <v>109</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3272,28 +3269,28 @@
         <v>113</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3314,7 +3311,7 @@
         <v>134</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
@@ -3325,10 +3322,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3351,19 +3348,19 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3388,31 +3385,31 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3430,10 +3427,10 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
@@ -3444,10 +3441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3473,65 +3470,65 @@
         <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="S18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T18" t="s" s="2">
+      <c r="U18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3549,24 +3546,24 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3589,16 +3586,16 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3612,43 +3609,43 @@
         <v>20</v>
       </c>
       <c r="T19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3657,7 +3654,7 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>101</v>
@@ -3666,24 +3663,24 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3706,13 +3703,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3763,7 +3760,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3781,24 +3778,24 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3821,16 +3818,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3880,7 +3877,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3898,27 +3895,27 @@
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>20</v>
@@ -3940,17 +3937,17 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3999,7 +3996,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4008,33 +4005,33 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4060,10 +4057,10 @@
         <v>91</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4114,7 +4111,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4123,19 +4120,19 @@
         <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4146,14 +4143,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4175,13 +4172,13 @@
         <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="N24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4222,7 +4219,7 @@
         <v>139</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
@@ -4231,7 +4228,7 @@
         <v>140</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4252,7 +4249,7 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4263,10 +4260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4292,16 +4289,16 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4329,28 +4326,28 @@
         <v>113</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4371,7 +4368,7 @@
         <v>134</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4382,10 +4379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4408,19 +4405,19 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4445,31 +4442,31 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4487,10 +4484,10 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4501,10 +4498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4530,65 +4527,65 @@
         <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4606,24 +4603,24 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4646,16 +4643,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4669,43 +4666,43 @@
         <v>20</v>
       </c>
       <c r="T28" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4714,7 +4711,7 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
@@ -4723,24 +4720,24 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4763,13 +4760,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4820,7 +4817,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4838,24 +4835,24 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4878,16 +4875,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4937,7 +4934,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4955,24 +4952,24 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4995,26 +4992,26 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="O31" t="s" s="2">
+      <c r="P31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q31" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="P31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q31" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="R31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5058,7 +5055,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5073,27 +5070,27 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5116,19 +5113,19 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5153,14 +5150,14 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5177,7 +5174,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5192,27 +5189,27 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5235,19 +5232,19 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5296,7 +5293,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5305,7 +5302,7 @@
         <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>101</v>
@@ -5314,24 +5311,24 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>291</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5354,19 +5351,19 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5415,7 +5412,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5436,7 +5433,7 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5447,10 +5444,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5473,17 +5470,17 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5532,7 +5529,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5553,7 +5550,7 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -5564,10 +5561,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5590,19 +5587,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5651,7 +5648,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5663,16 +5660,16 @@
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -5683,10 +5680,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5709,17 +5706,17 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5768,7 +5765,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5786,24 +5783,24 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5826,17 +5823,17 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -5885,7 +5882,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5906,7 +5903,7 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -5917,10 +5914,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5943,13 +5940,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6000,7 +5997,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6018,10 +6015,10 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6032,10 +6029,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6058,13 +6055,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6115,7 +6112,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6124,19 +6121,19 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6147,14 +6144,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6176,13 +6173,13 @@
         <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="N41" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6232,7 +6229,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6253,7 +6250,7 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6264,14 +6261,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6293,16 +6290,16 @@
         <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="N42" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O42" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6351,7 +6348,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6383,10 +6380,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6409,17 +6406,17 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6468,7 +6465,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6489,7 +6486,7 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6500,10 +6497,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6526,13 +6523,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6559,10 +6556,10 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>20</v>
@@ -6583,7 +6580,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>89</v>
@@ -6604,7 +6601,7 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6615,10 +6612,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6641,17 +6638,17 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6700,7 +6697,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6721,7 +6718,7 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -6732,10 +6729,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6758,13 +6755,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6815,7 +6812,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6836,7 +6833,7 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
